--- a/scenarios_attributes.xlsx
+++ b/scenarios_attributes.xlsx
@@ -633,7 +633,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -712,6 +712,9 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1448,8 +1451,8 @@
       <c r="F2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>17</v>
+      <c r="G2" s="34" t="s">
+        <v>16</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>18</v>
